--- a/TablasFacturas.xlsx
+++ b/TablasFacturas.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\Mercurius\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17260082-FF81-40A4-ABDA-8DD6C2887F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329BD214-568C-4BAE-8CCD-DFE6E3CD8AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5430" yWindow="0" windowWidth="25380" windowHeight="15480" activeTab="1" xr2:uid="{1087C9E4-1E08-4267-A264-DC0BE6EB7F9B}"/>
+    <workbookView xWindow="20025" yWindow="1545" windowWidth="16335" windowHeight="12195" xr2:uid="{1087C9E4-1E08-4267-A264-DC0BE6EB7F9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -238,66 +240,8 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Alvaro Padilla</author>
-  </authors>
-  <commentList>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{6B5EBC4E-B8E6-4800-A974-F886007A071A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Alvaro Padilla:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-1 Cada caracter &gt; se debe interpretar como un nivel de anidamiento. Por ejemplo: nombre es un elemento dentro de Emisor.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{69F24623-40CD-4B30-BDF2-CA61751A9E1D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Alvaro Padilla:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-2 En este caso, Tipo es un elementro dentro de Identificacion, el cual a su vez es un nodo de Emisor. Para mayor claridad referirse al schema.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="376">
   <si>
     <t>Condición del Campo</t>
   </si>
@@ -774,9 +718,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Código de Producto/servicio</t>
   </si>
   <si>
     <t xml:space="preserve">Tipo de Código de producto/servicio </t>
@@ -1450,6 +1391,9 @@
   </si>
   <si>
     <t>encuentren gravados del IVA, o desconozco la tarifa que puedo aplicar como crédito para cada actividad económica.</t>
+  </si>
+  <si>
+    <t>Código de Producto/servicio (CABYS)</t>
   </si>
 </sst>
 </file>
@@ -1484,12 +1428,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1504,11 +1454,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1539,8 +1490,8 @@
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1620276</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>705396</xdr:colOff>
       <xdr:row>143</xdr:row>
       <xdr:rowOff>95429</xdr:rowOff>
     </xdr:to>
@@ -1627,8 +1578,8 @@
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1182053</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>267173</xdr:colOff>
       <xdr:row>177</xdr:row>
       <xdr:rowOff>124309</xdr:rowOff>
     </xdr:to>
@@ -2111,8 +2062,8 @@
       <xdr:rowOff>176892</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>601789</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3866703</xdr:colOff>
       <xdr:row>317</xdr:row>
       <xdr:rowOff>158557</xdr:rowOff>
     </xdr:to>
@@ -2199,8 +2150,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>673906</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>5218692</xdr:colOff>
       <xdr:row>310</xdr:row>
       <xdr:rowOff>48137</xdr:rowOff>
     </xdr:to>
@@ -2359,6 +2310,857 @@
         <a:xfrm>
           <a:off x="530679" y="71696036"/>
           <a:ext cx="2448267" cy="866896"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>753250</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>162869</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D44AC10-85F0-0919-FEF4-3F90D53C3DD4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="114300" y="66675"/>
+          <a:ext cx="5553850" cy="6763694"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>181749</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>57813</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A1292DD-5518-A910-922B-8A89D3EDCD5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5705475" y="66675"/>
+          <a:ext cx="5544324" cy="4753638"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>210328</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>95460</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A187304-D3B7-0233-22BA-856E4EFEAA22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5705475" y="4876800"/>
+          <a:ext cx="5572903" cy="1505160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>419872</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>66941</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3A9CEBA-CD4A-9A13-0B69-E6837FF63CF0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11287125" y="66675"/>
+          <a:ext cx="5534797" cy="1905266"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>496084</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>171619</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagen 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BE2BF62-F469-C8F4-344C-D10EF5F6B0F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11277600" y="2009775"/>
+          <a:ext cx="5620534" cy="1209844"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>429400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>9685</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagen 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB94D000-3553-84AB-E6C5-93EFF1F4DF5C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11277600" y="3248025"/>
+          <a:ext cx="5553850" cy="1143160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>457976</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>105837</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57D06A04-3647-419F-570B-D54A15FEA41D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11296650" y="6019800"/>
+          <a:ext cx="5563376" cy="7611537"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>457976</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>85936</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagen 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77390E80-266B-6E29-12D0-3DE97B59BAC2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11296650" y="4476750"/>
+          <a:ext cx="5563376" cy="1514686"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>267474</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>76443</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2634788-8A79-A44C-2398-BE4EAB25CC07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="57150" y="47625"/>
+          <a:ext cx="5544324" cy="1743318"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>296053</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>20050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE9A76D5-6587-F0BC-0411-2C95CD74D73B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="57150" y="1809750"/>
+          <a:ext cx="5572903" cy="7163800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>315107</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>181932</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{716F66ED-99B3-AB72-8472-F3272354482E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="7800975"/>
+          <a:ext cx="5601482" cy="6858957"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>572279</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>9706</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE537865-63E8-6478-1EB3-988C48FF2127}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5657850" y="47625"/>
+          <a:ext cx="5582429" cy="1295581"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>572276</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>19337</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagen 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BCD0ECB-8802-B2A9-E2ED-093E181AA1AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5676900" y="1390650"/>
+          <a:ext cx="5563376" cy="2057687"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>543695</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>10236</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagen 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02A47844-F77C-9C36-97FB-113D9A6D081C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5695950" y="3486150"/>
+          <a:ext cx="5515745" cy="5096586"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>76974</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>124580</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A719555-A766-5DD1-7FE4-C26EB6E15A7E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11296650" y="47625"/>
+          <a:ext cx="5544324" cy="5410955"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>67446</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>171980</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagen 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BE577F1-28A8-0DE8-762D-08B42079B71D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11306175" y="5514975"/>
+          <a:ext cx="5525271" cy="3801005"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>248422</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>10238</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28E14042-9C7D-CF53-9B0C-98144209396B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="47625"/>
+          <a:ext cx="5534797" cy="5106113"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>496074</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>105048</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C073353-5A17-86BB-39F2-CF4211F42896}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5619750" y="57150"/>
+          <a:ext cx="5544324" cy="1952898"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>743724</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>58081</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3C43F93-FB1B-4772-DE6F-A23CE7BB4E51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11201400" y="57150"/>
+          <a:ext cx="5544324" cy="6668431"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2691,9 +3493,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="2" max="2" width="61.42578125" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.140625" customWidth="1"/>
+    <col min="5" max="5" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2702,36 +3504,36 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
       <c r="F3" t="s">
         <v>6</v>
       </c>
@@ -4283,7 +5085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>62</v>
       </c>
@@ -4317,6 +5119,9 @@
       <c r="K50">
         <v>2</v>
       </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="2"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -4334,7 +5139,7 @@
         <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F53">
         <v>2</v>
@@ -4366,7 +5171,7 @@
         <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -4395,10 +5200,10 @@
         <v>156</v>
       </c>
       <c r="C55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E55" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -4433,7 +5238,7 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F56">
         <v>4</v>
@@ -4459,7 +5264,7 @@
         <v>118</v>
       </c>
       <c r="B57" t="s">
-        <v>159</v>
+        <v>375</v>
       </c>
       <c r="C57" t="s">
         <v>22</v>
@@ -4468,7 +5273,7 @@
         <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F57">
         <v>2</v>
@@ -4500,7 +5305,7 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F58">
         <v>3</v>
@@ -4526,7 +5331,7 @@
         <v>120</v>
       </c>
       <c r="B59" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C59" t="s">
         <v>22</v>
@@ -4535,7 +5340,7 @@
         <v>2</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -4561,7 +5366,7 @@
         <v>121</v>
       </c>
       <c r="B60" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C60" t="s">
         <v>22</v>
@@ -4593,16 +5398,16 @@
         <v>122</v>
       </c>
       <c r="B61" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
+        <v>195</v>
+      </c>
+      <c r="D61" t="s">
         <v>196</v>
       </c>
-      <c r="D61" t="s">
-        <v>197</v>
-      </c>
       <c r="E61" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -4625,10 +5430,10 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B62" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C62" t="s">
         <v>22</v>
@@ -4637,7 +5442,7 @@
         <v>15</v>
       </c>
       <c r="E62" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F62">
         <v>1</v>
@@ -4663,7 +5468,7 @@
         <v>123</v>
       </c>
       <c r="B63" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C63" t="s">
         <v>22</v>
@@ -4672,7 +5477,7 @@
         <v>20</v>
       </c>
       <c r="E63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F63">
         <v>3</v>
@@ -4693,12 +5498,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>124</v>
       </c>
       <c r="B64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C64" t="s">
         <v>22</v>
@@ -4707,7 +5512,7 @@
         <v>200</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F64">
         <v>2</v>
@@ -4733,16 +5538,16 @@
         <v>125</v>
       </c>
       <c r="B65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C65" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D65" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -4768,16 +5573,16 @@
         <v>126</v>
       </c>
       <c r="B66" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C66" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D66" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E66" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -4806,7 +5611,7 @@
         <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F67">
         <v>3</v>
@@ -4832,16 +5637,16 @@
         <v>128</v>
       </c>
       <c r="B68" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C68" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D68" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E68" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F68">
         <v>2</v>
@@ -4867,7 +5672,7 @@
         <v>129</v>
       </c>
       <c r="B69" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C69" t="s">
         <v>22</v>
@@ -4876,7 +5681,7 @@
         <v>80</v>
       </c>
       <c r="E69" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F69">
         <v>2</v>
@@ -4902,16 +5707,16 @@
         <v>130</v>
       </c>
       <c r="B70" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C70" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D70" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E70" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -4937,16 +5742,16 @@
         <v>131</v>
       </c>
       <c r="B71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C71" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D71" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E71" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F71">
         <v>2</v>
@@ -4975,7 +5780,7 @@
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F72">
         <v>2</v>
@@ -5001,7 +5806,7 @@
         <v>121</v>
       </c>
       <c r="B73" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C73" t="s">
         <v>22</v>
@@ -5010,7 +5815,7 @@
         <v>2</v>
       </c>
       <c r="E73" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -5036,7 +5841,7 @@
         <v>133</v>
       </c>
       <c r="B74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C74" t="s">
         <v>22</v>
@@ -5045,7 +5850,7 @@
         <v>2</v>
       </c>
       <c r="E74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F74">
         <v>2</v>
@@ -5071,16 +5876,16 @@
         <v>134</v>
       </c>
       <c r="B75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C75" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D75" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E75" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F75">
         <v>2</v>
@@ -5106,16 +5911,16 @@
         <v>135</v>
       </c>
       <c r="B76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C76" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D76" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E76" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -5136,21 +5941,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="135" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>136</v>
       </c>
       <c r="B77" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C77" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -5176,16 +5981,16 @@
         <v>137</v>
       </c>
       <c r="B78" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C78" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D78" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E78" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F78">
         <v>4</v>
@@ -5211,13 +6016,13 @@
         <v>138</v>
       </c>
       <c r="B79" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F79">
         <v>2</v>
@@ -5243,7 +6048,7 @@
         <v>139</v>
       </c>
       <c r="B80" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C80" t="s">
         <v>22</v>
@@ -5252,7 +6057,7 @@
         <v>2</v>
       </c>
       <c r="E80" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -5270,12 +6075,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>140</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C81" t="s">
         <v>22</v>
@@ -5284,7 +6089,7 @@
         <v>40</v>
       </c>
       <c r="E81" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -5307,7 +6112,7 @@
         <v>141</v>
       </c>
       <c r="B82" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C82" t="s">
         <v>22</v>
@@ -5316,7 +6121,7 @@
         <v>160</v>
       </c>
       <c r="E82" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -5336,13 +6141,13 @@
         <v>142</v>
       </c>
       <c r="B83" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
       </c>
       <c r="E83" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -5362,16 +6167,16 @@
         <v>143</v>
       </c>
       <c r="B84" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C84" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -5394,16 +6199,16 @@
         <v>144</v>
       </c>
       <c r="B85" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C85" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E85" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F85">
         <v>1</v>
@@ -5421,21 +6226,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>145</v>
       </c>
       <c r="B86" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C86" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D86" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -5458,16 +6263,16 @@
         <v>146</v>
       </c>
       <c r="B87" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C87" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D87" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E87" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -5493,13 +6298,13 @@
         <v>147</v>
       </c>
       <c r="B88" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -5525,7 +6330,7 @@
         <v>148</v>
       </c>
       <c r="B89" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C89" t="s">
         <v>22</v>
@@ -5534,7 +6339,7 @@
         <v>2</v>
       </c>
       <c r="E89" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -5560,7 +6365,7 @@
         <v>149</v>
       </c>
       <c r="B90" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C90" t="s">
         <v>22</v>
@@ -5569,7 +6374,7 @@
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F90">
         <v>2</v>
@@ -5595,7 +6400,7 @@
         <v>150</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C91" t="s">
         <v>22</v>
@@ -5604,7 +6409,7 @@
         <v>100</v>
       </c>
       <c r="E91" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F91">
         <v>2</v>
@@ -5630,7 +6435,7 @@
         <v>151</v>
       </c>
       <c r="B92" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C92" t="s">
         <v>22</v>
@@ -5639,7 +6444,7 @@
         <v>160</v>
       </c>
       <c r="E92" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -5665,16 +6470,16 @@
         <v>152</v>
       </c>
       <c r="B93" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C93" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D93" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E93" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F93">
         <v>2</v>
@@ -5700,16 +6505,16 @@
         <v>153</v>
       </c>
       <c r="B94" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C94" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D94" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E94" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F94">
         <v>1</v>
@@ -5729,24 +6534,27 @@
       <c r="K94">
         <v>1</v>
       </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="2"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B97" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -5769,16 +6577,16 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B98" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
       </c>
       <c r="E98" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F98">
         <v>2</v>
@@ -5801,10 +6609,10 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B99" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C99" t="s">
         <v>22</v>
@@ -5813,7 +6621,7 @@
         <v>3</v>
       </c>
       <c r="E99" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -5836,19 +6644,19 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B100" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C100" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D100" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E100" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -5871,19 +6679,19 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B101" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C101" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D101" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E101" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -5906,19 +6714,19 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C102" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D102" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E102" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F102">
         <v>2</v>
@@ -5941,19 +6749,19 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C103" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D103" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E103" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F103">
         <v>2</v>
@@ -5976,19 +6784,19 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B104" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C104" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D104" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E104" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F104">
         <v>2</v>
@@ -6011,19 +6819,19 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B105" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C105" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D105" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E105" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F105">
         <v>2</v>
@@ -6046,19 +6854,19 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B106" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C106" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D106" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E106" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F106">
         <v>2</v>
@@ -6081,19 +6889,19 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B107" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C107" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D107" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E107" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F107">
         <v>2</v>
@@ -6116,19 +6924,19 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B108" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C108" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D108" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E108" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F108">
         <v>2</v>
@@ -6151,19 +6959,19 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B109" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C109" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D109" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E109" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F109">
         <v>2</v>
@@ -6186,19 +6994,19 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B110" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C110" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D110" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E110" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -6221,19 +7029,19 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B111" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C111" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D111" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E111" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F111">
         <v>2</v>
@@ -6256,19 +7064,19 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B112" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C112" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D112" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E112" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -6291,19 +7099,19 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B113" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C113" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D113" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E113" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F113">
         <v>2</v>
@@ -6326,19 +7134,19 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B114" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C114" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D114" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E114" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F114">
         <v>2</v>
@@ -6361,19 +7169,19 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B115" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C115" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D115" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E115" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F115">
         <v>2</v>
@@ -6396,19 +7204,19 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B116" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C116" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D116" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E116" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -6431,21 +7239,21 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B119" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
       </c>
       <c r="E119" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F119">
         <v>3</v>
@@ -6468,10 +7276,10 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B120" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C120" t="s">
         <v>22</v>
@@ -6480,7 +7288,7 @@
         <v>2</v>
       </c>
       <c r="E120" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F120">
         <v>1</v>
@@ -6503,10 +7311,10 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B121" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C121" t="s">
         <v>22</v>
@@ -6515,7 +7323,7 @@
         <v>50</v>
       </c>
       <c r="E121" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F121">
         <v>2</v>
@@ -6538,16 +7346,16 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B122" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C122" t="s">
         <v>23</v>
       </c>
       <c r="E122" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -6570,10 +7378,10 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B123" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C123" t="s">
         <v>22</v>
@@ -6582,7 +7390,7 @@
         <v>2</v>
       </c>
       <c r="E123" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F123">
         <v>2</v>
@@ -6605,10 +7413,10 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B124" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C124" t="s">
         <v>22</v>
@@ -6617,7 +7425,7 @@
         <v>180</v>
       </c>
       <c r="E124" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F124">
         <v>2</v>
@@ -6640,21 +7448,21 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B127" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C127" t="s">
         <v>24</v>
       </c>
       <c r="E127" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F127">
         <v>3</v>
@@ -6677,19 +7485,19 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B128" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C128" t="s">
         <v>22</v>
       </c>
       <c r="D128" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E128" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F128">
         <v>3</v>
@@ -6712,19 +7520,19 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B129" t="s">
+        <v>326</v>
+      </c>
+      <c r="C129" t="s">
         <v>327</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
         <v>328</v>
       </c>
-      <c r="D129" t="s">
-        <v>329</v>
-      </c>
       <c r="E129" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F129">
         <v>3</v>
@@ -6747,21 +7555,21 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="375" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="B132" t="s">
         <v>334</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>335</v>
       </c>
-      <c r="C132" t="s">
+      <c r="E132" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -6784,197 +7592,197 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -6988,393 +7796,43 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{131100C8-C416-4809-8EFF-10BEDB069C4B}">
-  <dimension ref="A1:P34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{131100C8-C416-4809-8EFF-10BEDB069C4B}">
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="39.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.7109375" customWidth="1"/>
     <col min="5" max="5" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" t="s">
-        <v>147</v>
-      </c>
-      <c r="H1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" t="s">
-        <v>148</v>
-      </c>
-      <c r="H2" t="s">
-        <v>116</v>
-      </c>
-      <c r="P2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H3" t="s">
-        <v>117</v>
-      </c>
-      <c r="P3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" t="s">
-        <v>150</v>
-      </c>
-      <c r="H4" t="s">
-        <v>118</v>
-      </c>
-      <c r="P4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H5" t="s">
-        <v>119</v>
-      </c>
-      <c r="P5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" t="s">
-        <v>152</v>
-      </c>
-      <c r="H6" t="s">
-        <v>120</v>
-      </c>
-      <c r="P6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" t="s">
-        <v>153</v>
-      </c>
-      <c r="H7" t="s">
-        <v>121</v>
-      </c>
-      <c r="P7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" t="s">
-        <v>59</v>
-      </c>
-      <c r="H17" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" t="s">
-        <v>46</v>
-      </c>
-      <c r="H18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" t="s">
-        <v>58</v>
-      </c>
-      <c r="H19" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="E20" t="s">
-        <v>59</v>
-      </c>
-      <c r="H20" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="E21" t="s">
-        <v>47</v>
-      </c>
-      <c r="H21" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H22" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H23" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H24" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="25" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H25" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="26" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H26" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H27" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H28" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="29" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H29" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H31" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="32" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H32" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H33" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H34" t="s">
-        <v>146</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3EEE43-068C-4F31-8019-CC364BA94859}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB6524D4-F512-4266-9C80-78DD9A77D1FB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/TablasFacturas.xlsx
+++ b/TablasFacturas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\Mercurius\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329BD214-568C-4BAE-8CCD-DFE6E3CD8AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734DCDC8-28B3-4A7D-AF7B-C5D35516E854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20025" yWindow="1545" windowWidth="16335" windowHeight="12195" xr2:uid="{1087C9E4-1E08-4267-A264-DC0BE6EB7F9B}"/>
+    <workbookView xWindow="21015" yWindow="1800" windowWidth="15915" windowHeight="11295" xr2:uid="{1087C9E4-1E08-4267-A264-DC0BE6EB7F9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1486,14 +1486,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>136</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>30816</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>705396</xdr:colOff>
       <xdr:row>143</xdr:row>
-      <xdr:rowOff>95429</xdr:rowOff>
+      <xdr:rowOff>173870</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1516,8 +1516,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="47625" y="31632525"/>
-          <a:ext cx="7354326" cy="1286054"/>
+          <a:off x="47625" y="31272816"/>
+          <a:ext cx="7358889" cy="1286054"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/TablasFacturas.xlsx
+++ b/TablasFacturas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\Mercurius\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734DCDC8-28B3-4A7D-AF7B-C5D35516E854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046DC530-3947-4461-BB36-CD6585D75158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21015" yWindow="1800" windowWidth="15915" windowHeight="11295" xr2:uid="{1087C9E4-1E08-4267-A264-DC0BE6EB7F9B}"/>
+    <workbookView xWindow="12900" yWindow="2490" windowWidth="22695" windowHeight="11295" xr2:uid="{1087C9E4-1E08-4267-A264-DC0BE6EB7F9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <author>Alvaro Padilla</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{28524C95-1256-4B84-AE4A-4A145E756AB7}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{28524C95-1256-4B84-AE4A-4A145E756AB7}">
       <text>
         <r>
           <rPr>
@@ -68,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{FB6A248A-28DD-404E-9614-9063DBABD670}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{FB6A248A-28DD-404E-9614-9063DBABD670}">
       <text>
         <r>
           <rPr>
@@ -92,7 +92,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{AAC24A3C-A2DA-4179-B78C-9B5D929428E1}">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{AAC24A3C-A2DA-4179-B78C-9B5D929428E1}">
       <text>
         <r>
           <rPr>
@@ -116,7 +116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{B471ECD8-520D-4C17-B2F3-DDC08E88EF40}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{B471ECD8-520D-4C17-B2F3-DDC08E88EF40}">
       <text>
         <r>
           <rPr>
@@ -140,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{B5AF3896-86F0-41D5-81D5-DF6F2821F0FA}">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{B5AF3896-86F0-41D5-81D5-DF6F2821F0FA}">
       <text>
         <r>
           <rPr>
@@ -164,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{281A22CE-5B27-487F-9643-6499A7982035}">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{281A22CE-5B27-487F-9643-6499A7982035}">
       <text>
         <r>
           <rPr>
@@ -188,7 +188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A9" authorId="0" shapeId="0" xr:uid="{E3663681-CC26-4592-AFBA-477DEBA19075}">
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{E3663681-CC26-4592-AFBA-477DEBA19075}">
       <text>
         <r>
           <rPr>
@@ -212,7 +212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{37584D20-EA6C-4820-85F1-45DAA5132423}">
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{37584D20-EA6C-4820-85F1-45DAA5132423}">
       <text>
         <r>
           <rPr>
@@ -1484,13 +1484,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>137</xdr:row>
       <xdr:rowOff>30816</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>705396</xdr:colOff>
       <xdr:row>143</xdr:row>
       <xdr:rowOff>173870</xdr:rowOff>
@@ -1528,13 +1528,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>151</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1105300</xdr:colOff>
       <xdr:row>157</xdr:row>
       <xdr:rowOff>9686</xdr:rowOff>
@@ -1572,13 +1572,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
       <xdr:row>159</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>267173</xdr:colOff>
       <xdr:row>177</xdr:row>
       <xdr:rowOff>124309</xdr:rowOff>
@@ -1616,13 +1616,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>180</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1838785</xdr:colOff>
       <xdr:row>195</xdr:row>
       <xdr:rowOff>76598</xdr:rowOff>
@@ -1660,13 +1660,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
       <xdr:row>197</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>2067437</xdr:colOff>
       <xdr:row>204</xdr:row>
       <xdr:rowOff>66868</xdr:rowOff>
@@ -1704,13 +1704,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
       <xdr:row>209</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1791184</xdr:colOff>
       <xdr:row>221</xdr:row>
       <xdr:rowOff>38412</xdr:rowOff>
@@ -1748,13 +1748,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
       <xdr:row>223</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>2000753</xdr:colOff>
       <xdr:row>234</xdr:row>
       <xdr:rowOff>38388</xdr:rowOff>
@@ -1792,13 +1792,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>236</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1495854</xdr:colOff>
       <xdr:row>242</xdr:row>
       <xdr:rowOff>145</xdr:rowOff>
@@ -1836,13 +1836,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>503464</xdr:colOff>
       <xdr:row>244</xdr:row>
       <xdr:rowOff>13607</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1106591</xdr:colOff>
       <xdr:row>258</xdr:row>
       <xdr:rowOff>156874</xdr:rowOff>
@@ -1880,13 +1880,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>272143</xdr:colOff>
       <xdr:row>262</xdr:row>
       <xdr:rowOff>149678</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1323008</xdr:colOff>
       <xdr:row>269</xdr:row>
       <xdr:rowOff>92706</xdr:rowOff>
@@ -1924,13 +1924,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>326572</xdr:colOff>
       <xdr:row>271</xdr:row>
       <xdr:rowOff>108858</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>215224</xdr:colOff>
       <xdr:row>274</xdr:row>
       <xdr:rowOff>108938</xdr:rowOff>
@@ -1968,13 +1968,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>244928</xdr:colOff>
       <xdr:row>276</xdr:row>
       <xdr:rowOff>136071</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>952845</xdr:colOff>
       <xdr:row>281</xdr:row>
       <xdr:rowOff>50467</xdr:rowOff>
@@ -2012,13 +2012,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>544286</xdr:colOff>
       <xdr:row>290</xdr:row>
       <xdr:rowOff>136071</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1299834</xdr:colOff>
       <xdr:row>301</xdr:row>
       <xdr:rowOff>31574</xdr:rowOff>
@@ -2056,13 +2056,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1333499</xdr:colOff>
       <xdr:row>290</xdr:row>
       <xdr:rowOff>176892</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>3866703</xdr:colOff>
       <xdr:row>317</xdr:row>
       <xdr:rowOff>158557</xdr:rowOff>
@@ -2100,13 +2100,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>54429</xdr:colOff>
       <xdr:row>290</xdr:row>
       <xdr:rowOff>176893</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>2597959</xdr:colOff>
       <xdr:row>317</xdr:row>
       <xdr:rowOff>177611</xdr:rowOff>
@@ -2144,13 +2144,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>2694215</xdr:colOff>
       <xdr:row>291</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>5218692</xdr:colOff>
       <xdr:row>310</xdr:row>
       <xdr:rowOff>48137</xdr:rowOff>
@@ -2188,13 +2188,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>653143</xdr:colOff>
       <xdr:row>321</xdr:row>
       <xdr:rowOff>176893</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1351533</xdr:colOff>
       <xdr:row>327</xdr:row>
       <xdr:rowOff>5579</xdr:rowOff>
@@ -2232,13 +2232,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>653143</xdr:colOff>
       <xdr:row>326</xdr:row>
       <xdr:rowOff>176893</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1351533</xdr:colOff>
       <xdr:row>329</xdr:row>
       <xdr:rowOff>91236</xdr:rowOff>
@@ -2276,13 +2276,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>530679</xdr:colOff>
       <xdr:row>334</xdr:row>
       <xdr:rowOff>13607</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1210017</xdr:colOff>
       <xdr:row>338</xdr:row>
       <xdr:rowOff>118503</xdr:rowOff>
@@ -3489,89 +3489,87 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D478C2-099E-4418-B988-E6F954066255}">
-  <dimension ref="A1:K348"/>
+  <dimension ref="B1:L348"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" customWidth="1"/>
-    <col min="2" max="2" width="61.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" customWidth="1"/>
+    <col min="3" max="3" width="61.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>7</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>9</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>10</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>28</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="G4">
         <v>1</v>
       </c>
@@ -3587,26 +3585,26 @@
       <c r="K4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>50</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
       <c r="G5">
         <v>1</v>
       </c>
@@ -3622,26 +3620,26 @@
       <c r="K5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>20</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>30</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
       <c r="G6">
         <v>1</v>
       </c>
@@ -3657,23 +3655,23 @@
       <c r="K6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>31</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
       <c r="G7">
         <v>1</v>
       </c>
@@ -3689,23 +3687,23 @@
       <c r="K7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
       <c r="G8">
         <v>1</v>
       </c>
@@ -3721,23 +3719,23 @@
       <c r="K8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>100</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
       <c r="G9">
         <v>1</v>
       </c>
@@ -3753,20 +3751,20 @@
       <c r="K9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>24</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>33</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
       <c r="G10">
         <v>1</v>
       </c>
@@ -3782,26 +3780,26 @@
       <c r="K10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>64</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>22</v>
       </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
         <v>87</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
       <c r="G11">
         <v>1</v>
       </c>
@@ -3817,26 +3815,26 @@
       <c r="K11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>35</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>65</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>22</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>12</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>88</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
       <c r="G12">
         <v>1</v>
       </c>
@@ -3852,26 +3850,26 @@
       <c r="K12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>66</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>22</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>80</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>89</v>
       </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
       <c r="G13">
         <v>2</v>
       </c>
@@ -3887,20 +3885,20 @@
       <c r="K13">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="L13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>24</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>90</v>
       </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
       <c r="G14">
         <v>1</v>
       </c>
@@ -3916,26 +3914,26 @@
       <c r="K14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="L14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
         <v>38</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>67</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>22</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
         <v>91</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
       <c r="G15">
         <v>1</v>
       </c>
@@ -3951,26 +3949,26 @@
       <c r="K15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="L15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
         <v>39</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>68</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>22</v>
       </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" t="s">
         <v>91</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
       <c r="G16">
         <v>1</v>
       </c>
@@ -3986,26 +3984,26 @@
       <c r="K16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="L16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
         <v>40</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>69</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>22</v>
       </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
         <v>91</v>
       </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
       <c r="G17">
         <v>1</v>
       </c>
@@ -4021,26 +4019,26 @@
       <c r="K17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="L17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
         <v>41</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>70</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>22</v>
       </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18" t="s">
         <v>91</v>
       </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
       <c r="G18">
         <v>2</v>
       </c>
@@ -4056,26 +4054,26 @@
       <c r="K18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="L18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
         <v>42</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>71</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>22</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>250</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>92</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
       <c r="G19">
         <v>1</v>
       </c>
@@ -4091,20 +4089,20 @@
       <c r="K19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="L19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
         <v>43</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>24</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>93</v>
       </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
       <c r="G20">
         <v>2</v>
       </c>
@@ -4120,26 +4118,26 @@
       <c r="K20">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="L20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
         <v>44</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>72</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>86</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>3</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>94</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
       <c r="G21">
         <v>1</v>
       </c>
@@ -4155,26 +4153,26 @@
       <c r="K21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="L21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>45</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>73</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>86</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>20</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>96</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
       <c r="G22">
         <v>1</v>
       </c>
@@ -4190,20 +4188,20 @@
       <c r="K22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="L22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
         <v>46</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>24</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>95</v>
       </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
       <c r="G23">
         <v>2</v>
       </c>
@@ -4219,26 +4217,26 @@
       <c r="K23">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="L23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>44</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>72</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>86</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>3</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>96</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
       <c r="G24">
         <v>1</v>
       </c>
@@ -4254,26 +4252,26 @@
       <c r="K24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="L24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
         <v>45</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>73</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>86</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>20</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>96</v>
       </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
       <c r="G25">
         <v>1</v>
       </c>
@@ -4289,26 +4287,26 @@
       <c r="K25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="L25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
         <v>47</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>74</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>22</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>160</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>97</v>
       </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
       <c r="G26">
         <v>1</v>
       </c>
@@ -4324,31 +4322,31 @@
       <c r="K26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="L26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
         <v>48</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>75</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>24</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>98</v>
       </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -4356,23 +4354,23 @@
       <c r="K27">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="L27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
         <v>49</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>76</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>22</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>100</v>
       </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
       <c r="G28">
         <v>1</v>
       </c>
@@ -4388,28 +4386,28 @@
       <c r="K28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="L28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
         <v>50</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>24</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>99</v>
       </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29">
         <v>2</v>
@@ -4417,26 +4415,26 @@
       <c r="K29">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="L29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
         <v>51</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>77</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>22</v>
       </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30" t="s">
         <v>100</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
       <c r="G30">
         <v>1</v>
       </c>
@@ -4452,26 +4450,26 @@
       <c r="K30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="L30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
         <v>35</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>78</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>22</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>12</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>101</v>
       </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
       <c r="G31">
         <v>1</v>
       </c>
@@ -4487,26 +4485,26 @@
       <c r="K31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="L31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
         <v>52</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>79</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>22</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>20</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>102</v>
       </c>
-      <c r="F32">
-        <v>2</v>
-      </c>
       <c r="G32">
         <v>2</v>
       </c>
@@ -4522,26 +4520,26 @@
       <c r="K32">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="L32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
         <v>53</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>80</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>22</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>80</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>103</v>
       </c>
-      <c r="F33">
-        <v>2</v>
-      </c>
       <c r="G33">
         <v>2</v>
       </c>
@@ -4557,26 +4555,26 @@
       <c r="K33">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="L33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>37</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>24</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>104</v>
       </c>
-      <c r="F34">
-        <v>2</v>
-      </c>
       <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34">
         <v>4</v>
       </c>
-      <c r="H34">
-        <v>2</v>
-      </c>
       <c r="I34">
         <v>2</v>
       </c>
@@ -4586,27 +4584,27 @@
       <c r="K34">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="L34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
         <v>54</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>67</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>22</v>
       </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
         <v>91</v>
       </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="H35">
+      <c r="G35">
         <v>1</v>
       </c>
       <c r="I35">
@@ -4618,27 +4616,27 @@
       <c r="K35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="L35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
         <v>39</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>68</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>22</v>
       </c>
-      <c r="D36">
-        <v>2</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36" t="s">
         <v>91</v>
       </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="H36">
+      <c r="G36">
         <v>1</v>
       </c>
       <c r="I36">
@@ -4650,27 +4648,27 @@
       <c r="K36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="L36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
         <v>40</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>69</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>22</v>
       </c>
-      <c r="D37">
-        <v>2</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37" t="s">
         <v>91</v>
       </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="H37">
+      <c r="G37">
         <v>1</v>
       </c>
       <c r="I37">
@@ -4682,27 +4680,27 @@
       <c r="K37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="L37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>55</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>70</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>22</v>
       </c>
-      <c r="D38">
-        <v>2</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38" t="s">
         <v>91</v>
       </c>
-      <c r="F38">
-        <v>2</v>
-      </c>
-      <c r="H38">
+      <c r="G38">
         <v>2</v>
       </c>
       <c r="I38">
@@ -4714,27 +4712,27 @@
       <c r="K38">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="L38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
         <v>42</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>71</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>22</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>160</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>92</v>
       </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="H39">
+      <c r="G39">
         <v>1</v>
       </c>
       <c r="I39">
@@ -4746,55 +4744,55 @@
       <c r="K39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="L39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
         <v>56</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>81</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>22</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>300</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>105</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>3</v>
       </c>
-      <c r="G40">
-        <v>2</v>
-      </c>
       <c r="H40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40">
         <v>3</v>
       </c>
       <c r="J40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="L40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
         <v>57</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>24</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>106</v>
       </c>
-      <c r="F41">
-        <v>2</v>
-      </c>
       <c r="G41">
         <v>2</v>
       </c>
@@ -4810,26 +4808,26 @@
       <c r="K41">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="L41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
         <v>58</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>72</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>86</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>3</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>94</v>
       </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
       <c r="G42">
         <v>1</v>
       </c>
@@ -4845,26 +4843,26 @@
       <c r="K42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="L42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
         <v>59</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>73</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>86</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>20</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>96</v>
       </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
       <c r="G43">
         <v>1</v>
       </c>
@@ -4880,20 +4878,20 @@
       <c r="K43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="L43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
         <v>46</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>24</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>107</v>
       </c>
-      <c r="F44">
-        <v>2</v>
-      </c>
       <c r="G44">
         <v>2</v>
       </c>
@@ -4909,26 +4907,26 @@
       <c r="K44">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="L44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
         <v>58</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>72</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>86</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>3</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>108</v>
       </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
       <c r="G45">
         <v>1</v>
       </c>
@@ -4944,26 +4942,26 @@
       <c r="K45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="L45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
         <v>59</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>73</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>86</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>20</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>108</v>
       </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
       <c r="G46">
         <v>1</v>
       </c>
@@ -4979,26 +4977,26 @@
       <c r="K46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="L46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
         <v>47</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>82</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>22</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>160</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>109</v>
       </c>
-      <c r="F47">
-        <v>2</v>
-      </c>
       <c r="G47">
         <v>2</v>
       </c>
@@ -5014,26 +5012,26 @@
       <c r="K47">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="L47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
         <v>60</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>83</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>22</v>
       </c>
-      <c r="D48">
-        <v>2</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48" t="s">
         <v>110</v>
       </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
       <c r="G48">
         <v>1</v>
       </c>
@@ -5049,26 +5047,26 @@
       <c r="K48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="L48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
         <v>61</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>84</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>22</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>10</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>111</v>
       </c>
-      <c r="F49">
-        <v>2</v>
-      </c>
       <c r="G49">
         <v>2</v>
       </c>
@@ -5084,26 +5082,26 @@
       <c r="K49">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="L49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
         <v>62</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>85</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>22</v>
       </c>
-      <c r="D50">
-        <v>2</v>
-      </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
       <c r="G50">
         <v>1</v>
       </c>
@@ -5114,44 +5112,44 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K50">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="L50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B51" s="2"/>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
         <v>114</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>154</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>24</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>201</v>
       </c>
-      <c r="F53">
-        <v>2</v>
-      </c>
       <c r="G53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J53">
         <v>2</v>
@@ -5159,23 +5157,23 @@
       <c r="K53">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="L53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
         <v>115</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>155</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>24</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>202</v>
       </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
       <c r="G54">
         <v>1</v>
       </c>
@@ -5191,23 +5189,23 @@
       <c r="K54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="L54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
         <v>116</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>156</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>194</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>203</v>
       </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
       <c r="G55">
         <v>1</v>
       </c>
@@ -5223,61 +5221,61 @@
       <c r="K55">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="L55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
         <v>117</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>157</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>22</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>12</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>204</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>4</v>
       </c>
-      <c r="G56">
-        <v>2</v>
-      </c>
       <c r="H56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I56">
         <v>4</v>
       </c>
       <c r="J56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K56">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="L56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
         <v>118</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>375</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>22</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>13</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>205</v>
       </c>
-      <c r="F57">
-        <v>2</v>
-      </c>
       <c r="G57">
         <v>2</v>
       </c>
@@ -5293,22 +5291,22 @@
       <c r="K57">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="L57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
         <v>119</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>158</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>24</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>206</v>
-      </c>
-      <c r="F58">
-        <v>3</v>
       </c>
       <c r="G58">
         <v>3</v>
@@ -5325,26 +5323,26 @@
       <c r="K58">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="L58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
         <v>120</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>159</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>22</v>
       </c>
-      <c r="D59">
-        <v>2</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
       <c r="G59">
         <v>1</v>
       </c>
@@ -5360,23 +5358,23 @@
       <c r="K59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="L59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
         <v>121</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>160</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>22</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>20</v>
       </c>
-      <c r="F60">
-        <v>2</v>
-      </c>
       <c r="G60">
         <v>2</v>
       </c>
@@ -5392,26 +5390,26 @@
       <c r="K60">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="L60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
         <v>122</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>161</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>195</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>196</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>208</v>
       </c>
-      <c r="F61">
-        <v>1</v>
-      </c>
       <c r="G61">
         <v>1</v>
       </c>
@@ -5427,26 +5425,26 @@
       <c r="K61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="L61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
         <v>164</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>162</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>22</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>15</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>209</v>
       </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
       <c r="G62">
         <v>1</v>
       </c>
@@ -5462,25 +5460,25 @@
       <c r="K62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="L62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
         <v>123</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>163</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>22</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <v>20</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>210</v>
-      </c>
-      <c r="F63">
-        <v>3</v>
       </c>
       <c r="G63">
         <v>3</v>
@@ -5497,34 +5495,34 @@
       <c r="K63">
         <v>3</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="L63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
         <v>124</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>165</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>22</v>
       </c>
-      <c r="D64">
+      <c r="E64">
         <v>200</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="F64" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F64">
-        <v>2</v>
-      </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64">
         <v>2</v>
@@ -5532,26 +5530,26 @@
       <c r="K64">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="L64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
         <v>125</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>166</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>195</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>197</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>212</v>
       </c>
-      <c r="F65">
-        <v>1</v>
-      </c>
       <c r="G65">
         <v>1</v>
       </c>
@@ -5567,26 +5565,26 @@
       <c r="K65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="L65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
         <v>126</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>167</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>195</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>197</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>213</v>
       </c>
-      <c r="F66">
-        <v>1</v>
-      </c>
       <c r="G66">
         <v>1</v>
       </c>
@@ -5602,19 +5600,19 @@
       <c r="K66">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="L66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
         <v>127</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>24</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>214</v>
-      </c>
-      <c r="F67">
-        <v>3</v>
       </c>
       <c r="G67">
         <v>3</v>
@@ -5631,26 +5629,26 @@
       <c r="K67">
         <v>3</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="L67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
         <v>128</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>168</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>195</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>197</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>215</v>
       </c>
-      <c r="F68">
-        <v>2</v>
-      </c>
       <c r="G68">
         <v>2</v>
       </c>
@@ -5666,26 +5664,26 @@
       <c r="K68">
         <v>2</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="L68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
         <v>129</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>169</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>22</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>80</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>216</v>
       </c>
-      <c r="F69">
-        <v>2</v>
-      </c>
       <c r="G69">
         <v>2</v>
       </c>
@@ -5701,26 +5699,26 @@
       <c r="K69">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="L69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
         <v>130</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>170</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>195</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>197</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>217</v>
       </c>
-      <c r="F70">
-        <v>1</v>
-      </c>
       <c r="G70">
         <v>1</v>
       </c>
@@ -5736,32 +5734,32 @@
       <c r="K70">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="L70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
         <v>131</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>171</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>195</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>197</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>218</v>
       </c>
-      <c r="F71">
-        <v>2</v>
-      </c>
       <c r="G71">
+        <v>2</v>
+      </c>
+      <c r="H71">
         <v>4</v>
       </c>
-      <c r="H71">
-        <v>2</v>
-      </c>
       <c r="I71">
         <v>2</v>
       </c>
@@ -5771,20 +5769,20 @@
       <c r="K71">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="L71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
         <v>132</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>24</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>219</v>
       </c>
-      <c r="F72">
-        <v>2</v>
-      </c>
       <c r="G72">
         <v>2</v>
       </c>
@@ -5800,31 +5798,31 @@
       <c r="K72">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="L72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
         <v>121</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>172</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>22</v>
       </c>
-      <c r="D73">
-        <v>2</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="F73" t="s">
         <v>220</v>
       </c>
-      <c r="F73">
-        <v>1</v>
-      </c>
       <c r="G73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I73">
         <v>1</v>
@@ -5835,26 +5833,26 @@
       <c r="K73">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="L73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
         <v>133</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>173</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>22</v>
       </c>
-      <c r="D74">
-        <v>2</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="F74" t="s">
         <v>221</v>
       </c>
-      <c r="F74">
-        <v>2</v>
-      </c>
       <c r="G74">
         <v>2</v>
       </c>
@@ -5870,26 +5868,26 @@
       <c r="K74">
         <v>2</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="L74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
         <v>134</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>174</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>195</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>198</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>222</v>
       </c>
-      <c r="F75">
-        <v>2</v>
-      </c>
       <c r="G75">
         <v>2</v>
       </c>
@@ -5905,26 +5903,26 @@
       <c r="K75">
         <v>2</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="L75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
         <v>135</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>175</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>195</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>199</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>223</v>
       </c>
-      <c r="F76">
-        <v>2</v>
-      </c>
       <c r="G76">
         <v>2</v>
       </c>
@@ -5940,26 +5938,26 @@
       <c r="K76">
         <v>2</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="L76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
         <v>136</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>176</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>195</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>197</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F77">
-        <v>1</v>
-      </c>
       <c r="G77">
         <v>1</v>
       </c>
@@ -5975,64 +5973,64 @@
       <c r="K77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="L77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
         <v>137</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>177</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>195</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>197</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>225</v>
       </c>
-      <c r="F78">
+      <c r="G78">
         <v>4</v>
       </c>
-      <c r="G78">
-        <v>2</v>
-      </c>
       <c r="H78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I78">
         <v>4</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K78">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="L78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
         <v>138</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>178</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>24</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>226</v>
       </c>
-      <c r="F79">
-        <v>2</v>
-      </c>
       <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="H79">
         <v>4</v>
       </c>
-      <c r="H79">
-        <v>2</v>
-      </c>
       <c r="I79">
         <v>2</v>
       </c>
@@ -6042,27 +6040,27 @@
       <c r="K79">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="L79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
         <v>139</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>179</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>22</v>
       </c>
-      <c r="D80">
-        <v>2</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="E80">
+        <v>2</v>
+      </c>
+      <c r="F80" t="s">
         <v>227</v>
       </c>
-      <c r="F80">
-        <v>1</v>
-      </c>
-      <c r="H80">
+      <c r="G80">
         <v>1</v>
       </c>
       <c r="I80">
@@ -6074,27 +6072,27 @@
       <c r="K80">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="L80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
         <v>140</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>22</v>
       </c>
-      <c r="D81">
+      <c r="E81">
         <v>40</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>228</v>
       </c>
-      <c r="F81">
-        <v>1</v>
-      </c>
-      <c r="H81">
+      <c r="G81">
         <v>1</v>
       </c>
       <c r="I81">
@@ -6106,82 +6104,82 @@
       <c r="K81">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="L81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
         <v>141</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>181</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>22</v>
       </c>
-      <c r="D82">
+      <c r="E82">
         <v>160</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>229</v>
       </c>
-      <c r="F82">
-        <v>1</v>
-      </c>
-      <c r="H82">
-        <v>1</v>
-      </c>
-      <c r="J82">
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="I82">
         <v>1</v>
       </c>
       <c r="K82">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="L82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
         <v>142</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>182</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>23</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>230</v>
       </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-      <c r="H83">
-        <v>1</v>
-      </c>
-      <c r="J83">
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="I83">
         <v>1</v>
       </c>
       <c r="K83">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="L83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
         <v>143</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>183</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>195</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>198</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>231</v>
       </c>
-      <c r="F84">
-        <v>1</v>
-      </c>
-      <c r="H84">
+      <c r="G84">
         <v>1</v>
       </c>
       <c r="I84">
@@ -6193,27 +6191,27 @@
       <c r="K84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="L84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
         <v>144</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>184</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>195</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>197</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>232</v>
       </c>
-      <c r="F85">
-        <v>1</v>
-      </c>
-      <c r="H85">
+      <c r="G85">
         <v>1</v>
       </c>
       <c r="I85">
@@ -6225,27 +6223,27 @@
       <c r="K85">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="L85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
         <v>145</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>185</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>195</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>197</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="F86" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F86">
-        <v>1</v>
-      </c>
-      <c r="H86">
+      <c r="G86">
         <v>1</v>
       </c>
       <c r="I86">
@@ -6257,26 +6255,26 @@
       <c r="K86">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="L86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
         <v>146</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>186</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>195</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>197</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>234</v>
       </c>
-      <c r="F87">
-        <v>1</v>
-      </c>
       <c r="G87">
         <v>1</v>
       </c>
@@ -6292,23 +6290,23 @@
       <c r="K87">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="L87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
         <v>147</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>187</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>24</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>235</v>
       </c>
-      <c r="F88">
-        <v>2</v>
-      </c>
       <c r="G88">
         <v>2</v>
       </c>
@@ -6324,26 +6322,26 @@
       <c r="K88">
         <v>2</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="L88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
         <v>148</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>188</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>22</v>
       </c>
-      <c r="D89">
-        <v>2</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="F89" t="s">
         <v>236</v>
       </c>
-      <c r="F89">
-        <v>1</v>
-      </c>
       <c r="G89">
         <v>1</v>
       </c>
@@ -6359,34 +6357,34 @@
       <c r="K89">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="L89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
         <v>149</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>189</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>22</v>
       </c>
-      <c r="D90">
+      <c r="E90">
         <v>12</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>238</v>
       </c>
-      <c r="F90">
-        <v>2</v>
-      </c>
       <c r="G90">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H90">
         <v>4</v>
       </c>
       <c r="I90">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J90">
         <v>2</v>
@@ -6394,34 +6392,34 @@
       <c r="K90">
         <v>2</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="L90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
         <v>150</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>22</v>
       </c>
-      <c r="D91">
+      <c r="E91">
         <v>100</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>237</v>
       </c>
-      <c r="F91">
-        <v>2</v>
-      </c>
       <c r="G91">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H91">
         <v>4</v>
       </c>
       <c r="I91">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J91">
         <v>2</v>
@@ -6429,26 +6427,26 @@
       <c r="K91">
         <v>2</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="L91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
         <v>151</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>191</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>22</v>
       </c>
-      <c r="D92">
+      <c r="E92">
         <v>160</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>239</v>
       </c>
-      <c r="F92">
-        <v>1</v>
-      </c>
       <c r="G92">
         <v>1</v>
       </c>
@@ -6464,26 +6462,26 @@
       <c r="K92">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="L92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
         <v>152</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>192</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>195</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>200</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>240</v>
       </c>
-      <c r="F93">
-        <v>2</v>
-      </c>
       <c r="G93">
         <v>2</v>
       </c>
@@ -6499,26 +6497,26 @@
       <c r="K93">
         <v>2</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="L93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
         <v>153</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>193</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>195</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>197</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>241</v>
       </c>
-      <c r="F94">
-        <v>1</v>
-      </c>
       <c r="G94">
         <v>1</v>
       </c>
@@ -6534,31 +6532,31 @@
       <c r="K94">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="2"/>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="L94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B95" s="2"/>
+    </row>
+    <row r="96" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
         <v>243</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>263</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>24</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>283</v>
       </c>
-      <c r="F97">
-        <v>1</v>
-      </c>
       <c r="G97">
         <v>1</v>
       </c>
@@ -6574,23 +6572,23 @@
       <c r="K97">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="L97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
         <v>244</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>264</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>24</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>284</v>
       </c>
-      <c r="F98">
-        <v>2</v>
-      </c>
       <c r="G98">
         <v>2</v>
       </c>
@@ -6606,26 +6604,26 @@
       <c r="K98">
         <v>2</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="L98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
         <v>245</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>265</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>22</v>
       </c>
-      <c r="D99">
+      <c r="E99">
         <v>3</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>285</v>
       </c>
-      <c r="F99">
-        <v>1</v>
-      </c>
       <c r="G99">
         <v>1</v>
       </c>
@@ -6636,31 +6634,31 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K99">
         <v>2</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="L99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
         <v>246</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>266</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>195</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>197</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>212</v>
       </c>
-      <c r="F100">
-        <v>1</v>
-      </c>
       <c r="G100">
         <v>1</v>
       </c>
@@ -6671,31 +6669,31 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K100">
         <v>2</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="L100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
         <v>247</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>267</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>195</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>197</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>286</v>
       </c>
-      <c r="F101">
-        <v>2</v>
-      </c>
       <c r="G101">
         <v>2</v>
       </c>
@@ -6711,26 +6709,26 @@
       <c r="K101">
         <v>2</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="L101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
         <v>248</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>195</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>197</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>287</v>
       </c>
-      <c r="F102">
-        <v>2</v>
-      </c>
       <c r="G102">
         <v>2</v>
       </c>
@@ -6746,32 +6744,32 @@
       <c r="K102">
         <v>2</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="L102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
         <v>249</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>195</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>197</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>288</v>
       </c>
-      <c r="F103">
-        <v>2</v>
-      </c>
       <c r="G103">
+        <v>2</v>
+      </c>
+      <c r="H103">
         <v>4</v>
       </c>
-      <c r="H103">
-        <v>2</v>
-      </c>
       <c r="I103">
         <v>2</v>
       </c>
@@ -6781,26 +6779,26 @@
       <c r="K103">
         <v>2</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="L103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
         <v>250</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
         <v>270</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>195</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>197</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>289</v>
       </c>
-      <c r="F104">
-        <v>2</v>
-      </c>
       <c r="G104">
         <v>2</v>
       </c>
@@ -6816,26 +6814,26 @@
       <c r="K104">
         <v>2</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="L104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
         <v>251</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>271</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>195</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>197</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>290</v>
       </c>
-      <c r="F105">
-        <v>2</v>
-      </c>
       <c r="G105">
         <v>2</v>
       </c>
@@ -6851,32 +6849,32 @@
       <c r="K105">
         <v>2</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="L105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
         <v>252</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>272</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>195</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>197</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>291</v>
       </c>
-      <c r="F106">
-        <v>2</v>
-      </c>
       <c r="G106">
+        <v>2</v>
+      </c>
+      <c r="H106">
         <v>4</v>
       </c>
-      <c r="H106">
-        <v>2</v>
-      </c>
       <c r="I106">
         <v>2</v>
       </c>
@@ -6886,26 +6884,26 @@
       <c r="K106">
         <v>2</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="L106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B107" t="s">
         <v>253</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>273</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>195</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>197</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>292</v>
       </c>
-      <c r="F107">
-        <v>2</v>
-      </c>
       <c r="G107">
         <v>2</v>
       </c>
@@ -6921,26 +6919,26 @@
       <c r="K107">
         <v>2</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="L107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
         <v>254</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>274</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>195</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>197</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>293</v>
       </c>
-      <c r="F108">
-        <v>2</v>
-      </c>
       <c r="G108">
         <v>2</v>
       </c>
@@ -6956,32 +6954,32 @@
       <c r="K108">
         <v>2</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="L108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
         <v>255</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>275</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>195</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>197</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>294</v>
       </c>
-      <c r="F109">
-        <v>2</v>
-      </c>
       <c r="G109">
+        <v>2</v>
+      </c>
+      <c r="H109">
         <v>4</v>
       </c>
-      <c r="H109">
-        <v>2</v>
-      </c>
       <c r="I109">
         <v>2</v>
       </c>
@@ -6991,26 +6989,26 @@
       <c r="K109">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="L109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
         <v>256</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>276</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>195</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>197</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>295</v>
       </c>
-      <c r="F110">
-        <v>1</v>
-      </c>
       <c r="G110">
         <v>1</v>
       </c>
@@ -7026,26 +7024,26 @@
       <c r="K110">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="L110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
         <v>257</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
         <v>277</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>195</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>197</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>296</v>
       </c>
-      <c r="F111">
-        <v>2</v>
-      </c>
       <c r="G111">
         <v>2</v>
       </c>
@@ -7061,26 +7059,26 @@
       <c r="K111">
         <v>2</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="L111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
         <v>258</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>278</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>195</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>197</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>297</v>
       </c>
-      <c r="F112">
-        <v>1</v>
-      </c>
       <c r="G112">
         <v>1</v>
       </c>
@@ -7096,26 +7094,26 @@
       <c r="K112">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="L112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
         <v>259</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>279</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
         <v>195</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
         <v>197</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
         <v>298</v>
       </c>
-      <c r="F113">
-        <v>2</v>
-      </c>
       <c r="G113">
         <v>2</v>
       </c>
@@ -7131,34 +7129,34 @@
       <c r="K113">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="L113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
         <v>260</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" t="s">
         <v>280</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>195</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>197</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>299</v>
       </c>
-      <c r="F114">
-        <v>2</v>
-      </c>
       <c r="G114">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H114">
         <v>4</v>
       </c>
       <c r="I114">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J114">
         <v>2</v>
@@ -7166,26 +7164,26 @@
       <c r="K114">
         <v>2</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="L114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
         <v>261</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>281</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>195</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>197</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>300</v>
       </c>
-      <c r="F115">
-        <v>2</v>
-      </c>
       <c r="G115">
         <v>2</v>
       </c>
@@ -7201,26 +7199,26 @@
       <c r="K115">
         <v>2</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="L115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
         <v>262</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" t="s">
         <v>282</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>195</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>197</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>301</v>
       </c>
-      <c r="F116">
-        <v>1</v>
-      </c>
       <c r="G116">
         <v>1</v>
       </c>
@@ -7236,27 +7234,27 @@
       <c r="K116">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="L116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
         <v>321</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
         <v>303</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>24</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>304</v>
-      </c>
-      <c r="F119">
-        <v>3</v>
       </c>
       <c r="G119">
         <v>3</v>
@@ -7268,31 +7266,31 @@
         <v>3</v>
       </c>
       <c r="J119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K119">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="L119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
         <v>305</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
         <v>310</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>22</v>
       </c>
-      <c r="D120">
-        <v>2</v>
-      </c>
-      <c r="E120" t="s">
+      <c r="E120">
+        <v>2</v>
+      </c>
+      <c r="F120" t="s">
         <v>315</v>
       </c>
-      <c r="F120">
-        <v>1</v>
-      </c>
       <c r="G120">
         <v>1</v>
       </c>
@@ -7308,26 +7306,26 @@
       <c r="K120">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="L120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
         <v>306</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" t="s">
         <v>311</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
         <v>22</v>
       </c>
-      <c r="D121">
+      <c r="E121">
         <v>50</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
         <v>316</v>
       </c>
-      <c r="F121">
-        <v>2</v>
-      </c>
       <c r="G121">
         <v>2</v>
       </c>
@@ -7343,23 +7341,23 @@
       <c r="K121">
         <v>2</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="L121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
         <v>307</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
         <v>312</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>23</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>317</v>
       </c>
-      <c r="F122">
-        <v>1</v>
-      </c>
       <c r="G122">
         <v>1</v>
       </c>
@@ -7375,26 +7373,26 @@
       <c r="K122">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="L122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
         <v>308</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>313</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
         <v>22</v>
       </c>
-      <c r="D123">
-        <v>2</v>
-      </c>
-      <c r="E123" t="s">
+      <c r="E123">
+        <v>2</v>
+      </c>
+      <c r="F123" t="s">
         <v>318</v>
       </c>
-      <c r="F123">
-        <v>2</v>
-      </c>
       <c r="G123">
         <v>2</v>
       </c>
@@ -7410,26 +7408,26 @@
       <c r="K123">
         <v>2</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="L123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
         <v>309</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
         <v>314</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
         <v>22</v>
       </c>
-      <c r="D124">
+      <c r="E124">
         <v>180</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>319</v>
       </c>
-      <c r="F124">
-        <v>2</v>
-      </c>
       <c r="G124">
         <v>2</v>
       </c>
@@ -7445,27 +7443,27 @@
       <c r="K124">
         <v>2</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="L124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>322</v>
-      </c>
+    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>322</v>
       </c>
       <c r="C127" t="s">
+        <v>322</v>
+      </c>
+      <c r="D127" t="s">
         <v>24</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>329</v>
-      </c>
-      <c r="F127">
-        <v>3</v>
       </c>
       <c r="G127">
         <v>3</v>
@@ -7482,25 +7480,25 @@
       <c r="K127">
         <v>3</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="L127">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
         <v>323</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>325</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
         <v>22</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>328</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>330</v>
-      </c>
-      <c r="F128">
-        <v>3</v>
       </c>
       <c r="G128">
         <v>3</v>
@@ -7517,25 +7515,25 @@
       <c r="K128">
         <v>3</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="L128">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
         <v>324</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>326</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
         <v>327</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
         <v>328</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>331</v>
-      </c>
-      <c r="F129">
-        <v>3</v>
       </c>
       <c r="G129">
         <v>3</v>
@@ -7552,28 +7550,28 @@
       <c r="K129">
         <v>3</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="L129">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="375" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+    <row r="132" spans="2:12" ht="375" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
         <v>333</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>334</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>335</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="F132" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="F132">
-        <v>1</v>
-      </c>
       <c r="G132">
         <v>1</v>
       </c>
@@ -7589,212 +7587,233 @@
       <c r="K132">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="L132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+    <row r="136" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+    <row r="137" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B137" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B180" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B197" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B206" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B208" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B209" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
+    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B223" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B236" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
+    <row r="244" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B244" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
+    <row r="261" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B261" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
+    <row r="262" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B262" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
+    <row r="271" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B271" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
+    <row r="276" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B276" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
+    <row r="283" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B283" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
+    <row r="284" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B284" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
+    <row r="286" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B286" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
+    <row r="288" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B288" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
+    <row r="290" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B290" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
+    <row r="321" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B321" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
+    <row r="332" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B332" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
+    <row r="334" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B334" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
+    <row r="340" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B340" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A341" t="s">
+    <row r="341" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B341" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
+    <row r="342" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B342" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
+    <row r="343" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B343" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
+    <row r="344" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B344" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
+    <row r="345" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B345" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
+    <row r="346" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B346" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A347" t="s">
+    <row r="347" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B347" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
+    <row r="348" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B348" t="s">
         <v>374</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="G2:L2"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="G3:L132">
+    <cfRule type="iconSet" priority="2">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4">
+    <cfRule type="iconSet" priority="1">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
   <drawing r:id="rId2"/>
